--- a/output/pdf_financials_xlsx/ATX.xlsx
+++ b/output/pdf_financials_xlsx/ATX.xlsx
@@ -55444,10 +55444,10 @@
         </is>
       </c>
       <c r="T466" s="5" t="n">
-        <v>29.464507</v>
+        <v>-29.464507</v>
       </c>
       <c r="U466" s="5" t="n">
-        <v>95.461794</v>
+        <v>-95.461794</v>
       </c>
     </row>
     <row r="467">
@@ -55648,10 +55648,10 @@
         </is>
       </c>
       <c r="T468" s="5" t="n">
-        <v>29.464507</v>
+        <v>-29.464507</v>
       </c>
       <c r="U468" s="5" t="n">
-        <v>94.939278</v>
+        <v>-94.939278</v>
       </c>
     </row>
     <row r="469">

--- a/output/pdf_financials_xlsx/ATX.xlsx
+++ b/output/pdf_financials_xlsx/ATX.xlsx
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.908013</v>
+        <v>2.244695</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.328145</v>
+        <v>1.127548</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0.445841</v>
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.908013</v>
+        <v>-2.244695</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>-1.127548</v>
@@ -1029,22 +1029,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.0167</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000346</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.029318</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.03486</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.002266</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
@@ -1071,13 +1071,13 @@
         <v>0</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-0.330589</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>-0.386206</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>-1.965118</v>
       </c>
     </row>
     <row r="13">
@@ -2019,22 +2019,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-2.283563</v>
+        <v>-2.300263</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.606609</v>
+        <v>-1.606955</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-5.321825</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-40.506735</v>
+        <v>-40.536053</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-12.430367</v>
+        <v>-12.465227</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-8.778798999999999</v>
+        <v>-8.781065</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-0.593849</v>
@@ -2061,13 +2061,13 @@
         <v>-10.05707</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-30.032521</v>
+        <v>-29.701932</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-95.461794</v>
+        <v>-95.075588</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-95.461794</v>
+        <v>-93.49667599999999</v>
       </c>
     </row>
     <row r="28">
@@ -2135,22 +2135,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.283563</v>
+        <v>-2.300263</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.606609</v>
+        <v>-1.606955</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-5.321825</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-40.506735</v>
+        <v>-40.536053</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-12.430367</v>
+        <v>-12.465227</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-8.778798999999999</v>
+        <v>-8.781065</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-0.591948</v>
@@ -2177,13 +2177,13 @@
         <v>-10.052936</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-29.891851</v>
+        <v>-29.561262</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-95.406766</v>
+        <v>-95.02056</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-95.344157</v>
+        <v>-93.37903900000001</v>
       </c>
     </row>
     <row r="30">
@@ -2442,28 +2442,28 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.765445</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.655721</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.853679</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>3.45153</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.497823</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.011243</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.022708</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.037308</v>
       </c>
       <c r="J34" s="1" t="inlineStr">
         <is>
@@ -2476,16 +2476,16 @@
         </is>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.209188</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.313167</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.166086</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>15.622682</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>13.168474</v>
@@ -2570,28 +2570,28 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.765445</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.655721</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.853679</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>3.45153</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>1.497823</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.011243</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.022708</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.037308</v>
       </c>
       <c r="J36" s="1" t="inlineStr">
         <is>
@@ -2604,16 +2604,16 @@
         </is>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.209188</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.313167</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.166086</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>15.622682</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>13.168474</v>
@@ -3344,22 +3344,22 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.88117</v>
+        <v>0.027491</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>3.518643</v>
+        <v>0.06711300000000001</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>3.939838</v>
+        <v>2.442015</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.119414</v>
+        <v>0.108171</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.246868</v>
+        <v>0.22416</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.037308</v>
+        <v>0</v>
       </c>
       <c r="J48" s="1" t="inlineStr">
         <is>
@@ -3372,16 +3372,16 @@
         </is>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.215855</v>
+        <v>0.006667</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.323416</v>
+        <v>0.010249</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.228302</v>
+        <v>0.062216</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>15.669863</v>
+        <v>0.047181</v>
       </c>
       <c r="P48" s="3" t="n">
         <v>0.7571600000000001</v>
@@ -11046,7 +11046,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">
@@ -16008,7 +16008,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -54452,7 +54452,7 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
@@ -66373,7 +66373,7 @@
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E578" s="5" t="n">
@@ -72466,14 +72466,14 @@
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E639" s="5" t="n">
-        <v>-2.244695</v>
+        <v>2.244695</v>
       </c>
       <c r="F639" s="5" t="n">
-        <v>-1.127548</v>
+        <v>1.127548</v>
       </c>
       <c r="G639" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/ATX.xlsx
+++ b/output/pdf_financials_xlsx/ATX.xlsx
@@ -742,31 +742,31 @@
         <v>0.318045</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.074462</v>
+        <v>0.286531</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.077944</v>
+        <v>0.265459</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.07469000000000001</v>
+        <v>0.25188</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.075434</v>
+        <v>0.274996</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.046238</v>
+        <v>0.192107</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.021883</v>
+        <v>0.044796</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.021736</v>
+        <v>0.13306</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.016999</v>
+        <v>0.084271</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.028736</v>
+        <v>0.07545200000000001</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>0</v>
@@ -858,7 +858,7 @@
         <v>0.589968</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0.253683</v>
+        <v>0.285688</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>0.367897</v>
@@ -870,7 +870,7 @@
         <v>0.288433</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.186927</v>
+        <v>0.207712</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>0.055919</v>
@@ -919,28 +919,28 @@
         <v>1.127548</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.445841</v>
+        <v>0.633356</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.492509</v>
+        <v>0.669699</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.363867</v>
+        <v>0.563429</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.233165</v>
+        <v>0.399819</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.077802</v>
+        <v>0.100715</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.072142</v>
+        <v>0.183466</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.052224</v>
+        <v>0.119496</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.093491</v>
+        <v>0.140207</v>
       </c>
       <c r="L10" s="3" t="n">
         <v>0.02441</v>
@@ -1798,10 +1798,8 @@
       <c r="C24" s="3" t="n">
         <v>-0.04</v>
       </c>
-      <c r="D24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D24" s="3" t="n">
+        <v>-0.09</v>
       </c>
       <c r="E24" s="1" t="inlineStr">
         <is>
@@ -1872,10 +1870,8 @@
       <c r="C25" s="3" t="n">
         <v>-0.04</v>
       </c>
-      <c r="D25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D25" s="3" t="n">
+        <v>-0.09</v>
       </c>
       <c r="E25" s="1" t="inlineStr">
         <is>
@@ -1946,10 +1942,8 @@
       <c r="C26" s="3" t="n">
         <v>40.165225</v>
       </c>
-      <c r="D26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D26" s="3" t="n">
+        <v>45.798056</v>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
@@ -13806,7 +13800,11 @@
           <t>Asset held for sale – Note 15</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>AssetsHeldForSale</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
@@ -16107,7 +16105,11 @@
           <t>Receivables – Note 5</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
@@ -17610,7 +17612,11 @@
           <t>Accounts payable and accrued liabilities – Notes 7 and 8 $</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
@@ -63566,7 +63572,11 @@
           <t>Management fees - Note 7</t>
         </is>
       </c>
-      <c r="D549" t="inlineStr"/>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E549" t="inlineStr">
         <is>
           <t>-</t>
@@ -65577,7 +65587,11 @@
           <t>Consulting - Note 7</t>
         </is>
       </c>
-      <c r="D570" t="inlineStr"/>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E570" t="inlineStr">
         <is>
           <t>-</t>
@@ -69262,7 +69276,11 @@
           <t>Management fees – Note 5</t>
         </is>
       </c>
-      <c r="D607" t="inlineStr"/>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E607" t="inlineStr">
         <is>
           <t>-</t>
@@ -70557,7 +70575,11 @@
           <t>Legal – Note 7</t>
         </is>
       </c>
-      <c r="D620" t="inlineStr"/>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E620" t="inlineStr">
         <is>
           <t>-</t>
@@ -70656,7 +70678,11 @@
           <t>Management fees – Note 7</t>
         </is>
       </c>
-      <c r="D621" t="inlineStr"/>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E621" t="inlineStr">
         <is>
           <t>-</t>
@@ -71157,7 +71183,11 @@
           <t>Recovery of future income taxes – Note 11</t>
         </is>
       </c>
-      <c r="D626" t="inlineStr"/>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E626" t="inlineStr">
         <is>
           <t>-</t>
@@ -71555,7 +71585,11 @@
           <t>Basic and diluted loss per common share - Note 2 $</t>
         </is>
       </c>
-      <c r="D630" t="inlineStr"/>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E630" t="inlineStr">
         <is>
           <t>-</t>
